--- a/samples/Trial_Balance_US_Jul-26.xlsx
+++ b/samples/Trial_Balance_US_Jul-26.xlsx
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>136185.9</v>
+        <v>704830.12</v>
       </c>
     </row>
     <row r="8">
@@ -464,7 +464,7 @@
         <v>Cash</v>
       </c>
       <c r="D8">
-        <v>526.05</v>
+        <v>510.27</v>
       </c>
     </row>
     <row r="9">
@@ -478,7 +478,7 @@
         <v>Accounts Receivable</v>
       </c>
       <c r="D9">
-        <v>177777.6</v>
+        <v>172444.27</v>
       </c>
     </row>
     <row r="10">
@@ -492,7 +492,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D10">
-        <v>11885.55</v>
+        <v>11528.98</v>
       </c>
     </row>
     <row r="11">
@@ -506,7 +506,7 @@
         <v>Other Current Asset</v>
       </c>
       <c r="D11">
-        <v>9337.2</v>
+        <v>9057.08</v>
       </c>
     </row>
     <row r="12">
@@ -520,7 +520,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D12">
-        <v>21858.75</v>
+        <v>21202.99</v>
       </c>
     </row>
     <row r="13">
@@ -534,7 +534,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D13">
-        <v>120000</v>
+        <v>2924500</v>
       </c>
     </row>
     <row r="14">
@@ -548,7 +548,7 @@
         <v>Fixed Asset</v>
       </c>
       <c r="D14">
-        <v>92133.9</v>
+        <v>89369.88</v>
       </c>
     </row>
     <row r="15">
@@ -562,7 +562,7 @@
         <v>Fixed Asset</v>
       </c>
       <c r="D15">
-        <v>-34069.5</v>
+        <v>-33047.42</v>
       </c>
     </row>
     <row r="16">
@@ -576,7 +576,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D16">
-        <v>5722.8</v>
+        <v>5551.12</v>
       </c>
     </row>
     <row r="17">
@@ -590,7 +590,7 @@
         <v>Accounts Payable</v>
       </c>
       <c r="D17">
-        <v>-52362.3</v>
+        <v>-50791.43</v>
       </c>
     </row>
     <row r="18">
@@ -604,7 +604,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D18">
-        <v>-26850</v>
+        <v>-26044.5</v>
       </c>
     </row>
     <row r="19">
@@ -618,7 +618,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D19">
-        <v>-12912.9</v>
+        <v>-12525.51</v>
       </c>
     </row>
     <row r="20">
@@ -632,7 +632,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D20">
-        <v>-10370.7</v>
+        <v>-10059.58</v>
       </c>
     </row>
     <row r="21">
@@ -646,7 +646,7 @@
         <v>Other Current Liability</v>
       </c>
       <c r="D21">
-        <v>-15200</v>
+        <v>-344350</v>
       </c>
     </row>
     <row r="22">
@@ -660,7 +660,7 @@
         <v>Equity</v>
       </c>
       <c r="D22">
-        <v>-226125</v>
+        <v>-2000000</v>
       </c>
     </row>
     <row r="23">
@@ -674,7 +674,7 @@
         <v>Equity</v>
       </c>
       <c r="D23">
-        <v>-120720</v>
+        <v>-1500000</v>
       </c>
     </row>
     <row r="24">
@@ -702,7 +702,7 @@
         <v>Income</v>
       </c>
       <c r="D25">
-        <v>-455715.6</v>
+        <v>-364572.48</v>
       </c>
     </row>
     <row r="26">
@@ -716,7 +716,7 @@
         <v>Other Income</v>
       </c>
       <c r="D26">
-        <v>-2867.1</v>
+        <v>-2293.68</v>
       </c>
     </row>
     <row r="27">
@@ -730,7 +730,7 @@
         <v>Cost Of Goods Sold</v>
       </c>
       <c r="D27">
-        <v>165194.1</v>
+        <v>132155.28</v>
       </c>
     </row>
     <row r="28">
@@ -744,7 +744,7 @@
         <v>Expense</v>
       </c>
       <c r="D28">
-        <v>142334.1</v>
+        <v>113867.28</v>
       </c>
     </row>
     <row r="29">
@@ -758,7 +758,7 @@
         <v>Expense</v>
       </c>
       <c r="D29">
-        <v>13239.6</v>
+        <v>10591.68</v>
       </c>
     </row>
     <row r="30">
@@ -772,7 +772,7 @@
         <v>Expense</v>
       </c>
       <c r="D30">
-        <v>18693</v>
+        <v>14954.4</v>
       </c>
     </row>
     <row r="31">
@@ -786,7 +786,7 @@
         <v>Expense</v>
       </c>
       <c r="D31">
-        <v>14550</v>
+        <v>11640</v>
       </c>
     </row>
     <row r="32">
@@ -800,7 +800,7 @@
         <v>Expense</v>
       </c>
       <c r="D32">
-        <v>23897.7</v>
+        <v>19118.16</v>
       </c>
     </row>
     <row r="33">
@@ -814,7 +814,7 @@
         <v>Expense</v>
       </c>
       <c r="D33">
-        <v>7981.8</v>
+        <v>6385.44</v>
       </c>
     </row>
     <row r="34">
@@ -828,7 +828,7 @@
         <v>Expense</v>
       </c>
       <c r="D34">
-        <v>40400</v>
+        <v>144000</v>
       </c>
     </row>
     <row r="35">
@@ -842,7 +842,7 @@
         <v>Expense</v>
       </c>
       <c r="D35">
-        <v>17487</v>
+        <v>13989.6</v>
       </c>
     </row>
     <row r="36">

--- a/samples/Trial_Balance_US_Jul-26.xlsx
+++ b/samples/Trial_Balance_US_Jul-26.xlsx
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>704830.12</v>
+        <v>2601365.8</v>
       </c>
     </row>
     <row r="8">
@@ -534,7 +534,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D13">
-        <v>2924500</v>
+        <v>1169800</v>
       </c>
     </row>
     <row r="14">
@@ -702,7 +702,7 @@
         <v>Income</v>
       </c>
       <c r="D25">
-        <v>-364572.48</v>
+        <v>-310814.02</v>
       </c>
     </row>
     <row r="26">
@@ -716,7 +716,7 @@
         <v>Other Income</v>
       </c>
       <c r="D26">
-        <v>-2293.68</v>
+        <v>-724.32</v>
       </c>
     </row>
     <row r="27">
@@ -730,7 +730,7 @@
         <v>Cost Of Goods Sold</v>
       </c>
       <c r="D27">
-        <v>132155.28</v>
+        <v>39574.37</v>
       </c>
     </row>
     <row r="28">
@@ -744,7 +744,7 @@
         <v>Expense</v>
       </c>
       <c r="D28">
-        <v>113867.28</v>
+        <v>34196.26</v>
       </c>
     </row>
     <row r="29">
@@ -758,7 +758,7 @@
         <v>Expense</v>
       </c>
       <c r="D29">
-        <v>10591.68</v>
+        <v>3177.5</v>
       </c>
     </row>
     <row r="30">
@@ -772,7 +772,7 @@
         <v>Expense</v>
       </c>
       <c r="D30">
-        <v>14954.4</v>
+        <v>4486.32</v>
       </c>
     </row>
     <row r="31">
@@ -786,7 +786,7 @@
         <v>Expense</v>
       </c>
       <c r="D31">
-        <v>11640</v>
+        <v>3456</v>
       </c>
     </row>
     <row r="32">
@@ -800,7 +800,7 @@
         <v>Expense</v>
       </c>
       <c r="D32">
-        <v>19118.16</v>
+        <v>5771.52</v>
       </c>
     </row>
     <row r="33">
@@ -814,7 +814,7 @@
         <v>Expense</v>
       </c>
       <c r="D33">
-        <v>6385.44</v>
+        <v>1879.49</v>
       </c>
     </row>
     <row r="34">
@@ -828,7 +828,7 @@
         <v>Expense</v>
       </c>
       <c r="D34">
-        <v>144000</v>
+        <v>172800</v>
       </c>
     </row>
     <row r="35">
@@ -842,7 +842,7 @@
         <v>Expense</v>
       </c>
       <c r="D35">
-        <v>13989.6</v>
+        <v>4196.88</v>
       </c>
     </row>
     <row r="36">

--- a/samples/Trial_Balance_US_Jul-26.xlsx
+++ b/samples/Trial_Balance_US_Jul-26.xlsx
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>2601365.8</v>
+        <v>2871832.47</v>
       </c>
     </row>
     <row r="8">
@@ -534,7 +534,7 @@
         <v>Other Asset</v>
       </c>
       <c r="D13">
-        <v>1169800</v>
+        <v>3899333.33</v>
       </c>
     </row>
     <row r="14">
@@ -660,7 +660,7 @@
         <v>Equity</v>
       </c>
       <c r="D22">
-        <v>-2000000</v>
+        <v>-5000000</v>
       </c>
     </row>
     <row r="23">

--- a/samples/Trial_Balance_US_Jul-26.xlsx
+++ b/samples/Trial_Balance_US_Jul-26.xlsx
@@ -450,7 +450,7 @@
         <v>Bank</v>
       </c>
       <c r="D7">
-        <v>2871832.47</v>
+        <v>2670317.91</v>
       </c>
     </row>
     <row r="8">
@@ -702,7 +702,7 @@
         <v>Income</v>
       </c>
       <c r="D25">
-        <v>-310814.02</v>
+        <v>-109299.46</v>
       </c>
     </row>
     <row r="26">
